--- a/artfynd/A 61401-2019 artfynd.xlsx
+++ b/artfynd/A 61401-2019 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY2"/>
+  <dimension ref="A1:AY7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -786,6 +786,561 @@
       <c r="AY2" t="inlineStr">
         <is>
           <t>Naturvärdesinventering Y-län</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>113679611</v>
+      </c>
+      <c r="B3" t="n">
+        <v>78234</v>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>185</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Violettgrå tagellav</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Bryoria nadvornikiana</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Nördbergsmyran, Ång</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>678395</v>
+      </c>
+      <c r="R3" t="n">
+        <v>7075109</v>
+      </c>
+      <c r="S3" t="n">
+        <v>10</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Örnsköldsvik</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Trehörningsjö</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2023-06-01</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>2023-06-01</t>
+        </is>
+      </c>
+      <c r="AD3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AS3" t="inlineStr">
+        <is>
+          <t>Tomas Rask</t>
+        </is>
+      </c>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>Helene Andersson</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>Helene Andersson, Tomas Rask</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Naturvärdesinventering </t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>113680972</v>
+      </c>
+      <c r="B4" t="n">
+        <v>90128</v>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Långtjärnhällorna, Ång</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>678512</v>
+      </c>
+      <c r="R4" t="n">
+        <v>7075012</v>
+      </c>
+      <c r="S4" t="n">
+        <v>10</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Örnsköldsvik</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Trehörningsjö</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2023-06-01</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2023-06-01</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AU4" t="inlineStr">
+        <is>
+          <t>Tomas Rask</t>
+        </is>
+      </c>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Helene Andersson</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Helene Andersson, Tomas Rask</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Naturvärdesinventering </t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>113680974</v>
+      </c>
+      <c r="B5" t="n">
+        <v>90128</v>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Långtjärnhällorna, Ång</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>678507</v>
+      </c>
+      <c r="R5" t="n">
+        <v>7075016</v>
+      </c>
+      <c r="S5" t="n">
+        <v>10</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Örnsköldsvik</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Trehörningsjö</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2023-06-01</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2023-06-01</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AU5" t="inlineStr">
+        <is>
+          <t>Tomas Rask</t>
+        </is>
+      </c>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Helene Andersson</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Helene Andersson, Tomas Rask</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Naturvärdesinventering </t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>113680973</v>
+      </c>
+      <c r="B6" t="n">
+        <v>90128</v>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Långtjärnhällorna, Ång</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>678527</v>
+      </c>
+      <c r="R6" t="n">
+        <v>7074942</v>
+      </c>
+      <c r="S6" t="n">
+        <v>10</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Örnsköldsvik</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Trehörningsjö</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2023-06-01</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2023-06-01</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AU6" t="inlineStr">
+        <is>
+          <t>Tomas Rask</t>
+        </is>
+      </c>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Helene Andersson</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Helene Andersson, Tomas Rask</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Naturvärdesinventering </t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>113679613</v>
+      </c>
+      <c r="B7" t="n">
+        <v>78199</v>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Nördbergsmyran, Ång</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>678429</v>
+      </c>
+      <c r="R7" t="n">
+        <v>7075164</v>
+      </c>
+      <c r="S7" t="n">
+        <v>10</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Örnsköldsvik</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Trehörningsjö</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2023-06-01</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2023-06-01</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AS7" t="inlineStr">
+        <is>
+          <t>Tomas Rask</t>
+        </is>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Helene Andersson</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Helene Andersson, Tomas Rask</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Naturvärdesinventering </t>
         </is>
       </c>
     </row>

--- a/artfynd/A 61401-2019 artfynd.xlsx
+++ b/artfynd/A 61401-2019 artfynd.xlsx
@@ -791,10 +791,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>113679611</v>
+        <v>113679613</v>
       </c>
       <c r="B3" t="n">
-        <v>78234</v>
+        <v>78201</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -807,21 +807,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -831,10 +831,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>678395</v>
+        <v>678429</v>
       </c>
       <c r="R3" t="n">
-        <v>7075109</v>
+        <v>7075164</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -902,10 +902,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>113680972</v>
+        <v>113679611</v>
       </c>
       <c r="B4" t="n">
-        <v>90128</v>
+        <v>78236</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -918,34 +918,34 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1202</v>
+        <v>185</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Långtjärnhällorna, Ång</t>
+          <t>Nördbergsmyran, Ång</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>678512</v>
+        <v>678395</v>
       </c>
       <c r="R4" t="n">
-        <v>7075012</v>
+        <v>7075109</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -989,12 +989,12 @@
       <c r="AG4" t="b">
         <v>0</v>
       </c>
+      <c r="AS4" t="inlineStr">
+        <is>
+          <t>Tomas Rask</t>
+        </is>
+      </c>
       <c r="AT4" t="inlineStr"/>
-      <c r="AU4" t="inlineStr">
-        <is>
-          <t>Tomas Rask</t>
-        </is>
-      </c>
       <c r="AW4" t="inlineStr">
         <is>
           <t>Helene Andersson</t>
@@ -1013,10 +1013,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>113680974</v>
+        <v>113680973</v>
       </c>
       <c r="B5" t="n">
-        <v>90128</v>
+        <v>90130</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1053,10 +1053,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>678507</v>
+        <v>678527</v>
       </c>
       <c r="R5" t="n">
-        <v>7075016</v>
+        <v>7074942</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1124,10 +1124,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>113680973</v>
+        <v>113680974</v>
       </c>
       <c r="B6" t="n">
-        <v>90128</v>
+        <v>90130</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1164,10 +1164,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>678527</v>
+        <v>678507</v>
       </c>
       <c r="R6" t="n">
-        <v>7074942</v>
+        <v>7075016</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1235,10 +1235,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>113679613</v>
+        <v>113680972</v>
       </c>
       <c r="B7" t="n">
-        <v>78199</v>
+        <v>90130</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1251,34 +1251,34 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Nördbergsmyran, Ång</t>
+          <t>Långtjärnhällorna, Ång</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>678429</v>
+        <v>678512</v>
       </c>
       <c r="R7" t="n">
-        <v>7075164</v>
+        <v>7075012</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1322,12 +1322,12 @@
       <c r="AG7" t="b">
         <v>0</v>
       </c>
-      <c r="AS7" t="inlineStr">
+      <c r="AT7" t="inlineStr"/>
+      <c r="AU7" t="inlineStr">
         <is>
           <t>Tomas Rask</t>
         </is>
       </c>
-      <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
           <t>Helene Andersson</t>

--- a/artfynd/A 61401-2019 artfynd.xlsx
+++ b/artfynd/A 61401-2019 artfynd.xlsx
@@ -791,10 +791,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>113679613</v>
+        <v>113680972</v>
       </c>
       <c r="B3" t="n">
-        <v>78201</v>
+        <v>90131</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -807,34 +807,34 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Nördbergsmyran, Ång</t>
+          <t>Långtjärnhällorna, Ång</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>678429</v>
+        <v>678512</v>
       </c>
       <c r="R3" t="n">
-        <v>7075164</v>
+        <v>7075012</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -878,12 +878,12 @@
       <c r="AG3" t="b">
         <v>0</v>
       </c>
-      <c r="AS3" t="inlineStr">
+      <c r="AT3" t="inlineStr"/>
+      <c r="AU3" t="inlineStr">
         <is>
           <t>Tomas Rask</t>
         </is>
       </c>
-      <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
           <t>Helene Andersson</t>
@@ -1013,10 +1013,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>113680973</v>
+        <v>113679613</v>
       </c>
       <c r="B5" t="n">
-        <v>90130</v>
+        <v>78201</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1029,34 +1029,34 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Långtjärnhällorna, Ång</t>
+          <t>Nördbergsmyran, Ång</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>678527</v>
+        <v>678429</v>
       </c>
       <c r="R5" t="n">
-        <v>7074942</v>
+        <v>7075164</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1100,12 +1100,12 @@
       <c r="AG5" t="b">
         <v>0</v>
       </c>
+      <c r="AS5" t="inlineStr">
+        <is>
+          <t>Tomas Rask</t>
+        </is>
+      </c>
       <c r="AT5" t="inlineStr"/>
-      <c r="AU5" t="inlineStr">
-        <is>
-          <t>Tomas Rask</t>
-        </is>
-      </c>
       <c r="AW5" t="inlineStr">
         <is>
           <t>Helene Andersson</t>
@@ -1127,7 +1127,7 @@
         <v>113680974</v>
       </c>
       <c r="B6" t="n">
-        <v>90130</v>
+        <v>90131</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1235,10 +1235,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>113680972</v>
+        <v>113680973</v>
       </c>
       <c r="B7" t="n">
-        <v>90130</v>
+        <v>90131</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1275,10 +1275,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>678512</v>
+        <v>678527</v>
       </c>
       <c r="R7" t="n">
-        <v>7075012</v>
+        <v>7074942</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>

--- a/artfynd/A 61401-2019 artfynd.xlsx
+++ b/artfynd/A 61401-2019 artfynd.xlsx
@@ -791,10 +791,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>113680972</v>
+        <v>113679611</v>
       </c>
       <c r="B3" t="n">
-        <v>90131</v>
+        <v>78236</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -807,34 +807,34 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1202</v>
+        <v>185</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Långtjärnhällorna, Ång</t>
+          <t>Nördbergsmyran, Ång</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>678512</v>
+        <v>678395</v>
       </c>
       <c r="R3" t="n">
-        <v>7075012</v>
+        <v>7075109</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -878,12 +878,12 @@
       <c r="AG3" t="b">
         <v>0</v>
       </c>
+      <c r="AS3" t="inlineStr">
+        <is>
+          <t>Tomas Rask</t>
+        </is>
+      </c>
       <c r="AT3" t="inlineStr"/>
-      <c r="AU3" t="inlineStr">
-        <is>
-          <t>Tomas Rask</t>
-        </is>
-      </c>
       <c r="AW3" t="inlineStr">
         <is>
           <t>Helene Andersson</t>
@@ -902,10 +902,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>113679611</v>
+        <v>113679613</v>
       </c>
       <c r="B4" t="n">
-        <v>78236</v>
+        <v>78201</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -918,21 +918,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -942,10 +942,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>678395</v>
+        <v>678429</v>
       </c>
       <c r="R4" t="n">
-        <v>7075109</v>
+        <v>7075164</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1013,10 +1013,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>113679613</v>
+        <v>113680973</v>
       </c>
       <c r="B5" t="n">
-        <v>78201</v>
+        <v>90135</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1029,34 +1029,34 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Nördbergsmyran, Ång</t>
+          <t>Långtjärnhällorna, Ång</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>678429</v>
+        <v>678527</v>
       </c>
       <c r="R5" t="n">
-        <v>7075164</v>
+        <v>7074942</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1100,12 +1100,12 @@
       <c r="AG5" t="b">
         <v>0</v>
       </c>
-      <c r="AS5" t="inlineStr">
+      <c r="AT5" t="inlineStr"/>
+      <c r="AU5" t="inlineStr">
         <is>
           <t>Tomas Rask</t>
         </is>
       </c>
-      <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
           <t>Helene Andersson</t>
@@ -1127,7 +1127,7 @@
         <v>113680974</v>
       </c>
       <c r="B6" t="n">
-        <v>90131</v>
+        <v>90135</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1235,10 +1235,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>113680973</v>
+        <v>113680972</v>
       </c>
       <c r="B7" t="n">
-        <v>90131</v>
+        <v>90135</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1275,10 +1275,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>678527</v>
+        <v>678512</v>
       </c>
       <c r="R7" t="n">
-        <v>7074942</v>
+        <v>7075012</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>

--- a/artfynd/A 61401-2019 artfynd.xlsx
+++ b/artfynd/A 61401-2019 artfynd.xlsx
@@ -791,10 +791,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>113679611</v>
+        <v>113680972</v>
       </c>
       <c r="B3" t="n">
-        <v>78236</v>
+        <v>90135</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -807,34 +807,34 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>185</v>
+        <v>1202</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Nördbergsmyran, Ång</t>
+          <t>Långtjärnhällorna, Ång</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>678395</v>
+        <v>678512</v>
       </c>
       <c r="R3" t="n">
-        <v>7075109</v>
+        <v>7075012</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -878,12 +878,12 @@
       <c r="AG3" t="b">
         <v>0</v>
       </c>
-      <c r="AS3" t="inlineStr">
+      <c r="AT3" t="inlineStr"/>
+      <c r="AU3" t="inlineStr">
         <is>
           <t>Tomas Rask</t>
         </is>
       </c>
-      <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
           <t>Helene Andersson</t>
@@ -902,10 +902,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>113679613</v>
+        <v>113680974</v>
       </c>
       <c r="B4" t="n">
-        <v>78201</v>
+        <v>90135</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -918,34 +918,34 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Nördbergsmyran, Ång</t>
+          <t>Långtjärnhällorna, Ång</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>678429</v>
+        <v>678507</v>
       </c>
       <c r="R4" t="n">
-        <v>7075164</v>
+        <v>7075016</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -989,12 +989,12 @@
       <c r="AG4" t="b">
         <v>0</v>
       </c>
-      <c r="AS4" t="inlineStr">
+      <c r="AT4" t="inlineStr"/>
+      <c r="AU4" t="inlineStr">
         <is>
           <t>Tomas Rask</t>
         </is>
       </c>
-      <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
           <t>Helene Andersson</t>
@@ -1013,10 +1013,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>113680973</v>
+        <v>113679611</v>
       </c>
       <c r="B5" t="n">
-        <v>90135</v>
+        <v>78236</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1029,34 +1029,34 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1202</v>
+        <v>185</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Långtjärnhällorna, Ång</t>
+          <t>Nördbergsmyran, Ång</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>678527</v>
+        <v>678395</v>
       </c>
       <c r="R5" t="n">
-        <v>7074942</v>
+        <v>7075109</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1100,12 +1100,12 @@
       <c r="AG5" t="b">
         <v>0</v>
       </c>
+      <c r="AS5" t="inlineStr">
+        <is>
+          <t>Tomas Rask</t>
+        </is>
+      </c>
       <c r="AT5" t="inlineStr"/>
-      <c r="AU5" t="inlineStr">
-        <is>
-          <t>Tomas Rask</t>
-        </is>
-      </c>
       <c r="AW5" t="inlineStr">
         <is>
           <t>Helene Andersson</t>
@@ -1124,7 +1124,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>113680974</v>
+        <v>113680973</v>
       </c>
       <c r="B6" t="n">
         <v>90135</v>
@@ -1164,10 +1164,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>678507</v>
+        <v>678527</v>
       </c>
       <c r="R6" t="n">
-        <v>7075016</v>
+        <v>7074942</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1235,10 +1235,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>113680972</v>
+        <v>113679613</v>
       </c>
       <c r="B7" t="n">
-        <v>90135</v>
+        <v>78201</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1251,34 +1251,34 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Långtjärnhällorna, Ång</t>
+          <t>Nördbergsmyran, Ång</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>678512</v>
+        <v>678429</v>
       </c>
       <c r="R7" t="n">
-        <v>7075012</v>
+        <v>7075164</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1322,12 +1322,12 @@
       <c r="AG7" t="b">
         <v>0</v>
       </c>
+      <c r="AS7" t="inlineStr">
+        <is>
+          <t>Tomas Rask</t>
+        </is>
+      </c>
       <c r="AT7" t="inlineStr"/>
-      <c r="AU7" t="inlineStr">
-        <is>
-          <t>Tomas Rask</t>
-        </is>
-      </c>
       <c r="AW7" t="inlineStr">
         <is>
           <t>Helene Andersson</t>

--- a/artfynd/A 61401-2019 artfynd.xlsx
+++ b/artfynd/A 61401-2019 artfynd.xlsx
@@ -902,7 +902,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>113680974</v>
+        <v>113680973</v>
       </c>
       <c r="B4" t="n">
         <v>90135</v>
@@ -942,10 +942,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>678507</v>
+        <v>678527</v>
       </c>
       <c r="R4" t="n">
-        <v>7075016</v>
+        <v>7074942</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1013,10 +1013,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>113679611</v>
+        <v>113680974</v>
       </c>
       <c r="B5" t="n">
-        <v>78236</v>
+        <v>90135</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1029,34 +1029,34 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>185</v>
+        <v>1202</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Nördbergsmyran, Ång</t>
+          <t>Långtjärnhällorna, Ång</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>678395</v>
+        <v>678507</v>
       </c>
       <c r="R5" t="n">
-        <v>7075109</v>
+        <v>7075016</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1100,12 +1100,12 @@
       <c r="AG5" t="b">
         <v>0</v>
       </c>
-      <c r="AS5" t="inlineStr">
+      <c r="AT5" t="inlineStr"/>
+      <c r="AU5" t="inlineStr">
         <is>
           <t>Tomas Rask</t>
         </is>
       </c>
-      <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
           <t>Helene Andersson</t>
@@ -1124,10 +1124,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>113680973</v>
+        <v>113679613</v>
       </c>
       <c r="B6" t="n">
-        <v>90135</v>
+        <v>78201</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1140,34 +1140,34 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Långtjärnhällorna, Ång</t>
+          <t>Nördbergsmyran, Ång</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>678527</v>
+        <v>678429</v>
       </c>
       <c r="R6" t="n">
-        <v>7074942</v>
+        <v>7075164</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1211,12 +1211,12 @@
       <c r="AG6" t="b">
         <v>0</v>
       </c>
+      <c r="AS6" t="inlineStr">
+        <is>
+          <t>Tomas Rask</t>
+        </is>
+      </c>
       <c r="AT6" t="inlineStr"/>
-      <c r="AU6" t="inlineStr">
-        <is>
-          <t>Tomas Rask</t>
-        </is>
-      </c>
       <c r="AW6" t="inlineStr">
         <is>
           <t>Helene Andersson</t>
@@ -1235,10 +1235,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>113679613</v>
+        <v>113679611</v>
       </c>
       <c r="B7" t="n">
-        <v>78201</v>
+        <v>78236</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1251,21 +1251,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1275,10 +1275,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>678429</v>
+        <v>678395</v>
       </c>
       <c r="R7" t="n">
-        <v>7075164</v>
+        <v>7075109</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>

--- a/artfynd/A 61401-2019 artfynd.xlsx
+++ b/artfynd/A 61401-2019 artfynd.xlsx
@@ -791,10 +791,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>113680972</v>
+        <v>113679613</v>
       </c>
       <c r="B3" t="n">
-        <v>90135</v>
+        <v>78201</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -807,34 +807,34 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Långtjärnhällorna, Ång</t>
+          <t>Nördbergsmyran, Ång</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>678512</v>
+        <v>678429</v>
       </c>
       <c r="R3" t="n">
-        <v>7075012</v>
+        <v>7075164</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -878,12 +878,12 @@
       <c r="AG3" t="b">
         <v>0</v>
       </c>
+      <c r="AS3" t="inlineStr">
+        <is>
+          <t>Tomas Rask</t>
+        </is>
+      </c>
       <c r="AT3" t="inlineStr"/>
-      <c r="AU3" t="inlineStr">
-        <is>
-          <t>Tomas Rask</t>
-        </is>
-      </c>
       <c r="AW3" t="inlineStr">
         <is>
           <t>Helene Andersson</t>
@@ -902,7 +902,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>113680973</v>
+        <v>113680972</v>
       </c>
       <c r="B4" t="n">
         <v>90135</v>
@@ -942,10 +942,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>678527</v>
+        <v>678512</v>
       </c>
       <c r="R4" t="n">
-        <v>7074942</v>
+        <v>7075012</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1013,10 +1013,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>113680974</v>
+        <v>113679611</v>
       </c>
       <c r="B5" t="n">
-        <v>90135</v>
+        <v>78236</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1029,34 +1029,34 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1202</v>
+        <v>185</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Långtjärnhällorna, Ång</t>
+          <t>Nördbergsmyran, Ång</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>678507</v>
+        <v>678395</v>
       </c>
       <c r="R5" t="n">
-        <v>7075016</v>
+        <v>7075109</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1100,12 +1100,12 @@
       <c r="AG5" t="b">
         <v>0</v>
       </c>
+      <c r="AS5" t="inlineStr">
+        <is>
+          <t>Tomas Rask</t>
+        </is>
+      </c>
       <c r="AT5" t="inlineStr"/>
-      <c r="AU5" t="inlineStr">
-        <is>
-          <t>Tomas Rask</t>
-        </is>
-      </c>
       <c r="AW5" t="inlineStr">
         <is>
           <t>Helene Andersson</t>
@@ -1124,10 +1124,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>113679613</v>
+        <v>113680973</v>
       </c>
       <c r="B6" t="n">
-        <v>78201</v>
+        <v>90135</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1140,34 +1140,34 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Nördbergsmyran, Ång</t>
+          <t>Långtjärnhällorna, Ång</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>678429</v>
+        <v>678527</v>
       </c>
       <c r="R6" t="n">
-        <v>7075164</v>
+        <v>7074942</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1211,12 +1211,12 @@
       <c r="AG6" t="b">
         <v>0</v>
       </c>
-      <c r="AS6" t="inlineStr">
+      <c r="AT6" t="inlineStr"/>
+      <c r="AU6" t="inlineStr">
         <is>
           <t>Tomas Rask</t>
         </is>
       </c>
-      <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
           <t>Helene Andersson</t>
@@ -1235,10 +1235,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>113679611</v>
+        <v>113680974</v>
       </c>
       <c r="B7" t="n">
-        <v>78236</v>
+        <v>90135</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1251,34 +1251,34 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>185</v>
+        <v>1202</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Nördbergsmyran, Ång</t>
+          <t>Långtjärnhällorna, Ång</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>678395</v>
+        <v>678507</v>
       </c>
       <c r="R7" t="n">
-        <v>7075109</v>
+        <v>7075016</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1322,12 +1322,12 @@
       <c r="AG7" t="b">
         <v>0</v>
       </c>
-      <c r="AS7" t="inlineStr">
+      <c r="AT7" t="inlineStr"/>
+      <c r="AU7" t="inlineStr">
         <is>
           <t>Tomas Rask</t>
         </is>
       </c>
-      <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
           <t>Helene Andersson</t>

--- a/artfynd/A 61401-2019 artfynd.xlsx
+++ b/artfynd/A 61401-2019 artfynd.xlsx
@@ -791,10 +791,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>113679613</v>
+        <v>113679611</v>
       </c>
       <c r="B3" t="n">
-        <v>78201</v>
+        <v>78236</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -807,21 +807,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -831,10 +831,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>678429</v>
+        <v>678395</v>
       </c>
       <c r="R3" t="n">
-        <v>7075164</v>
+        <v>7075109</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -1013,10 +1013,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>113679611</v>
+        <v>113680973</v>
       </c>
       <c r="B5" t="n">
-        <v>78236</v>
+        <v>90135</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1029,34 +1029,34 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>185</v>
+        <v>1202</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Nördbergsmyran, Ång</t>
+          <t>Långtjärnhällorna, Ång</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>678395</v>
+        <v>678527</v>
       </c>
       <c r="R5" t="n">
-        <v>7075109</v>
+        <v>7074942</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1100,12 +1100,12 @@
       <c r="AG5" t="b">
         <v>0</v>
       </c>
-      <c r="AS5" t="inlineStr">
+      <c r="AT5" t="inlineStr"/>
+      <c r="AU5" t="inlineStr">
         <is>
           <t>Tomas Rask</t>
         </is>
       </c>
-      <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
           <t>Helene Andersson</t>
@@ -1124,7 +1124,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>113680973</v>
+        <v>113680974</v>
       </c>
       <c r="B6" t="n">
         <v>90135</v>
@@ -1164,10 +1164,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>678527</v>
+        <v>678507</v>
       </c>
       <c r="R6" t="n">
-        <v>7074942</v>
+        <v>7075016</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1235,10 +1235,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>113680974</v>
+        <v>113679613</v>
       </c>
       <c r="B7" t="n">
-        <v>90135</v>
+        <v>78201</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1251,34 +1251,34 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Långtjärnhällorna, Ång</t>
+          <t>Nördbergsmyran, Ång</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>678507</v>
+        <v>678429</v>
       </c>
       <c r="R7" t="n">
-        <v>7075016</v>
+        <v>7075164</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1322,12 +1322,12 @@
       <c r="AG7" t="b">
         <v>0</v>
       </c>
+      <c r="AS7" t="inlineStr">
+        <is>
+          <t>Tomas Rask</t>
+        </is>
+      </c>
       <c r="AT7" t="inlineStr"/>
-      <c r="AU7" t="inlineStr">
-        <is>
-          <t>Tomas Rask</t>
-        </is>
-      </c>
       <c r="AW7" t="inlineStr">
         <is>
           <t>Helene Andersson</t>

--- a/artfynd/A 61401-2019 artfynd.xlsx
+++ b/artfynd/A 61401-2019 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">
